--- a/data/AG/廠商代碼.xlsx
+++ b/data/AG/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1233"/>
+  <dimension ref="A1:B1234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15224,6 +15224,18 @@
         </is>
       </c>
     </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>C74</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>恆利毛織家</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/AG/廠商代碼.xlsx
+++ b/data/AG/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1234"/>
+  <dimension ref="A1:B1235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15236,6 +15236,18 @@
         </is>
       </c>
     </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>C75</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>平凡</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/AG/廠商代碼.xlsx
+++ b/data/AG/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1235"/>
+  <dimension ref="A1:B1236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15248,6 +15248,18 @@
         </is>
       </c>
     </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>C64</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>佰麗美</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/AG/廠商代碼.xlsx
+++ b/data/AG/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1236"/>
+  <dimension ref="A1:B1237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15260,6 +15260,18 @@
         </is>
       </c>
     </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>B41</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>CC服飾.花裙</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/AG/廠商代碼.xlsx
+++ b/data/AG/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1237"/>
+  <dimension ref="A1:B1238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15272,6 +15272,18 @@
         </is>
       </c>
     </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>DV</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/AG/廠商代碼.xlsx
+++ b/data/AG/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1238"/>
+  <dimension ref="A1:B1239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15284,6 +15284,18 @@
         </is>
       </c>
     </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>伊影</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
